--- a/data/trans_dic/P56$familiar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 31,6</t>
+          <t>9,33; 30,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 38,69</t>
+          <t>15,25; 38,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 33,24</t>
+          <t>12,33; 32,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,62; 66,65</t>
+          <t>48,93; 67,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 29,68</t>
+          <t>10,91; 28,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 36,07</t>
+          <t>22,74; 36,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,08; 39,31</t>
+          <t>22,22; 38,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,72; 63,45</t>
+          <t>53,96; 63,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 27,21</t>
+          <t>12,46; 26,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 33,77</t>
+          <t>22,79; 34,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,82; 34,61</t>
+          <t>21,42; 34,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,91; 62,63</t>
+          <t>54,03; 62,61</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,34</t>
+          <t>0,0; 55,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,81; 50,19</t>
+          <t>22,38; 49,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,66</t>
+          <t>0,0; 65,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,72</t>
+          <t>8,12; 55,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,99; 57,31</t>
+          <t>35,71; 57,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 63,05</t>
+          <t>7,0; 55,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 45,94</t>
+          <t>9,59; 48,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,36</t>
+          <t>0,0; 14,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 50,38</t>
+          <t>33,82; 51,32</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 58,24</t>
+          <t>7,19; 60,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 62,93</t>
+          <t>8,85; 65,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,03</t>
+          <t>0,0; 79,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 52,52</t>
+          <t>12,54; 49,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,15</t>
+          <t>10,28; 33,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 37,43</t>
+          <t>16,04; 38,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 26,46</t>
+          <t>9,76; 25,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,39; 58,12</t>
+          <t>42,84; 58,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,09</t>
+          <t>10,87; 28,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 35,69</t>
+          <t>23,27; 36,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 33,24</t>
+          <t>18,22; 32,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,79; 60,55</t>
+          <t>51,18; 60,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 26,2</t>
+          <t>12,54; 26,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,86; 33,94</t>
+          <t>23,18; 34,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 29,64</t>
+          <t>17,63; 28,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,69; 58,65</t>
+          <t>50,36; 58,07</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4168; 13948</t>
+          <t>4119; 13673</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10539; 26459</t>
+          <t>10430; 26227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7161; 18846</t>
+          <t>6991; 18536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33696; 45260</t>
+          <t>33227; 45790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9588; 24759</t>
+          <t>9098; 24110</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42720; 67065</t>
+          <t>42291; 68762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31510; 56115</t>
+          <t>31717; 55250</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107733; 127248</t>
+          <t>108227; 127233</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16253; 34701</t>
+          <t>15896; 34104</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57598; 85888</t>
+          <t>57970; 86561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41526; 69014</t>
+          <t>42724; 69279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>144719; 168136</t>
+          <t>145043; 168095</t>
         </is>
       </c>
     </row>
@@ -1717,57 +1717,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5963</t>
+          <t>0; 5056</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1622</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5912; 13603</t>
+          <t>6064; 13470</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4512</t>
+          <t>0; 4461</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6437</t>
+          <t>955; 6481</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4749</t>
+          <t>0; 5129</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15141; 24113</t>
+          <t>15026; 24265</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>826; 6881</t>
+          <t>764; 6078</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1954; 9597</t>
+          <t>2003; 10136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5615</t>
+          <t>0; 5126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23095; 34850</t>
+          <t>23393; 35502</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1925,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>225; 986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>501; 3771</t>
+          <t>466; 3896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>563; 4071</t>
+          <t>573; 4214</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>0; 4277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1748; 6799</t>
+          <t>1623; 6449</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5379; 15524</t>
+          <t>4961; 16299</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12799; 29383</t>
+          <t>12593; 29885</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7052; 19077</t>
+          <t>7036; 18674</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44035; 58984</t>
+          <t>43476; 59017</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10506; 25341</t>
+          <t>10165; 26329</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46323; 72145</t>
+          <t>47028; 73133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32633; 57110</t>
+          <t>31293; 56105</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>129010; 150842</t>
+          <t>127485; 150062</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18898; 37160</t>
+          <t>17788; 37377</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64167; 95258</t>
+          <t>65057; 95954</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43864; 72276</t>
+          <t>42987; 70377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>177704; 205634</t>
+          <t>176554; 203581</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 30,98</t>
+          <t>9,38; 31,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 38,35</t>
+          <t>15,82; 38,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 32,7</t>
+          <t>13,51; 34,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,93; 67,43</t>
+          <t>49,42; 67,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 28,9</t>
+          <t>11,4; 30,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,74; 36,98</t>
+          <t>22,96; 36,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,22; 38,71</t>
+          <t>21,7; 38,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,96; 63,44</t>
+          <t>53,92; 63,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 26,74</t>
+          <t>12,58; 26,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,79; 34,03</t>
+          <t>22,92; 34,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,42; 34,74</t>
+          <t>20,98; 35,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,03; 62,61</t>
+          <t>54,09; 63,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,82</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,41</t>
+          <t>0,0; 55,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,38; 49,7</t>
+          <t>20,86; 50,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,91</t>
+          <t>0,0; 66,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 55,09</t>
+          <t>8,03; 54,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,2</t>
+          <t>0,0; 21,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,71; 57,67</t>
+          <t>34,62; 54,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 55,69</t>
+          <t>7,18; 57,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 48,52</t>
+          <t>9,64; 48,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,02</t>
+          <t>0,0; 15,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 51,32</t>
+          <t>32,66; 50,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 60,17</t>
+          <t>7,55; 61,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 65,14</t>
+          <t>7,99; 60,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,07</t>
+          <t>0,0; 79,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 49,82</t>
+          <t>13,41; 48,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 33,76</t>
+          <t>11,73; 33,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,07</t>
+          <t>17,48; 38,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,9</t>
+          <t>9,72; 26,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,84; 58,15</t>
+          <t>42,21; 57,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,15</t>
+          <t>10,32; 27,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 36,18</t>
+          <t>22,73; 35,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 32,66</t>
+          <t>17,83; 32,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,18; 60,24</t>
+          <t>50,83; 59,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,54; 26,35</t>
+          <t>12,78; 26,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 34,19</t>
+          <t>23,26; 34,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 28,86</t>
+          <t>17,31; 29,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,36; 58,07</t>
+          <t>49,98; 57,61</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39824</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>127446</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>169450</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4119; 13673</t>
+          <t>4139; 13680</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10430; 26227</t>
+          <t>10818; 26440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6991; 18536</t>
+          <t>7660; 19687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33227; 45790</t>
+          <t>35705; 48969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9098; 24110</t>
+          <t>9510; 25052</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42291; 68762</t>
+          <t>42686; 67598</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31717; 55250</t>
+          <t>30978; 54882</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>108227; 127233</t>
+          <t>117105; 137364</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15896; 34104</t>
+          <t>16045; 34420</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57970; 86561</t>
+          <t>58302; 86829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42724; 69279</t>
+          <t>41840; 70378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>145043; 168095</t>
+          <t>156558; 182892</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>31397</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3351</t>
+          <t>0; 4146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5056</t>
+          <t>0; 5087</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1727,47 +1727,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6064; 13470</t>
+          <t>5964; 14372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>955; 6481</t>
+          <t>944; 6425</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5129</t>
+          <t>0; 5460</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15026; 24265</t>
+          <t>16637; 26205</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>764; 6078</t>
+          <t>783; 6311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2003; 10136</t>
+          <t>2013; 10146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5126</t>
+          <t>0; 5577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23393; 35502</t>
+          <t>25035; 38325</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4246</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>466; 3896</t>
+          <t>540; 4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>573; 4214</t>
+          <t>653; 4905</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4277</t>
+          <t>0; 4275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1623; 6449</t>
+          <t>2053; 7431</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>139491</t>
+          <t>151307</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>190644</t>
+          <t>205094</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4961; 16299</t>
+          <t>5663; 16148</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12593; 29885</t>
+          <t>13724; 29980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7036; 18674</t>
+          <t>7008; 19030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43476; 59017</t>
+          <t>45578; 62386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10165; 26329</t>
+          <t>9655; 25607</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47028; 73133</t>
+          <t>45949; 71941</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31293; 56105</t>
+          <t>30624; 55836</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>127485; 150062</t>
+          <t>138967; 162859</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17788; 37377</t>
+          <t>18120; 37429</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65057; 95954</t>
+          <t>65267; 95582</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42987; 70377</t>
+          <t>42208; 71623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>176554; 203581</t>
+          <t>190634; 219723</t>
         </is>
       </c>
     </row>
